--- a/data/Proyectos_Bauvek.xlsx
+++ b/data/Proyectos_Bauvek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04993CD-11AC-4631-9D46-3022D026B4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9235E7D7-BA9D-45B0-A3E2-C159673A3E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="115">
   <si>
     <t>Proyecto</t>
   </si>
@@ -56,6 +56,12 @@
     <t>Comitente</t>
   </si>
   <si>
+    <t>m² Construidos cubierta</t>
+  </si>
+  <si>
+    <t>m² Construidos semicubierta</t>
+  </si>
+  <si>
     <t>m² Terreno</t>
   </si>
   <si>
@@ -83,49 +89,55 @@
     <t>Córdoba</t>
   </si>
   <si>
+    <t>Villa ciudad parque - Molvento</t>
+  </si>
+  <si>
+    <t>Vivienda Hermanos Rossi.xml</t>
+  </si>
+  <si>
+    <t>253 tareas / 27% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Julieta Santiago</t>
+  </si>
+  <si>
+    <t>JULIETA SANTIAGO - IVAN PETRINI</t>
+  </si>
+  <si>
+    <t>Vivienda Julieta Santiago.xml</t>
+  </si>
+  <si>
+    <t>248 tareas / 41% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Esteban y Matías</t>
+  </si>
+  <si>
+    <t>La Calera - Vistas de la Deseada</t>
+  </si>
+  <si>
+    <t>Esteban y Matías</t>
+  </si>
+  <si>
+    <t>Vivienda Esteban y Matias.xml</t>
+  </si>
+  <si>
+    <t>232 tareas / 1% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Roberto Conde</t>
+  </si>
+  <si>
+    <t>En pausa</t>
+  </si>
+  <si>
+    <t>2-En Proyecto</t>
+  </si>
+  <si>
     <t>Molvento</t>
   </si>
   <si>
-    <t>Vivienda_Hermanos_Rossi.xml</t>
-  </si>
-  <si>
-    <t>253 tareas / 27% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Julieta Santiago</t>
-  </si>
-  <si>
-    <t>JULIETA SANTIAGO - IVAN PETRINI</t>
-  </si>
-  <si>
-    <t>Vivienda_Julieta_Santiago.xml</t>
-  </si>
-  <si>
-    <t>248 tareas / 41% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Esteban y Matías</t>
-  </si>
-  <si>
-    <t>Esteban y Matías</t>
-  </si>
-  <si>
-    <t>Vivienda_Esteban_y_Matias.xml</t>
-  </si>
-  <si>
-    <t>232 tareas / 1% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Roberto Conde</t>
-  </si>
-  <si>
-    <t>En pausa</t>
-  </si>
-  <si>
-    <t>2-En Proyecto</t>
-  </si>
-  <si>
-    <t>Vivienda_Roberto_Conde.xml</t>
+    <t>Vivienda RC.xml</t>
   </si>
   <si>
     <t>225 tareas / 7% avance</t>
@@ -134,10 +146,13 @@
     <t>Vivienda Lugón</t>
   </si>
   <si>
+    <t>Mendiolaza - Q2</t>
+  </si>
+  <si>
     <t>RODRIGO LUGON</t>
   </si>
   <si>
-    <t>Vivienda_Lugon.xml</t>
+    <t>Vivienda Lugon.xml</t>
   </si>
   <si>
     <t>179 tareas / 1% avance</t>
@@ -146,13 +161,13 @@
     <t>Vivienda Reboni</t>
   </si>
   <si>
-    <t>Mendiolaza</t>
+    <t>Mendiolaza - El terrón</t>
   </si>
   <si>
     <t>Hernan Reboni</t>
   </si>
   <si>
-    <t>Vivienda_Reboni.xml</t>
+    <t>Vivienda Reboni.xml</t>
   </si>
   <si>
     <t>178 tareas / 47% avance</t>
@@ -164,10 +179,13 @@
     <t>Chubut</t>
   </si>
   <si>
+    <t>Malagueño - Cañitas</t>
+  </si>
+  <si>
     <t>Venturelli-Bernal</t>
   </si>
   <si>
-    <t>Vivienda_Venturelli_-_Bernal.xml</t>
+    <t>Vivienda Venturelli-Bernal.xml</t>
   </si>
   <si>
     <t>106 tareas / 8% avance</t>
@@ -176,7 +194,7 @@
     <t>La Vicenta</t>
   </si>
   <si>
-    <t>La_Vicenta.xml</t>
+    <t>Loteo - La Vicenta.xml</t>
   </si>
   <si>
     <t>49 tareas / 15% avance</t>
@@ -188,7 +206,7 @@
     <t>Agustin Zampol</t>
   </si>
   <si>
-    <t>Vivienda_AZ.xml</t>
+    <t>Vivienda AZ.xml</t>
   </si>
   <si>
     <t>32 tareas / 0% avance</t>
@@ -197,7 +215,7 @@
     <t>Losa Mogetta</t>
   </si>
   <si>
-    <t>Losa_Mogetta.xml</t>
+    <t>Losa Mogetta.xml</t>
   </si>
   <si>
     <t>19 tareas / 87% avance</t>
@@ -209,31 +227,160 @@
     <t>Rodolfo Subias y Melisa Lew</t>
   </si>
   <si>
-    <t>Vivienda_Lew-Subias.xml</t>
+    <t>Vivienda Lew-Subias.xml</t>
   </si>
   <si>
     <t>5 tareas / 24% avance</t>
   </si>
   <si>
-    <t>m² Construidos semicubierta</t>
-  </si>
-  <si>
-    <t>m² Construidos cubierta</t>
-  </si>
-  <si>
-    <t>Mendiolaza - El terrón</t>
-  </si>
-  <si>
-    <t>La Calera - Vistas de la Deseada</t>
-  </si>
-  <si>
-    <t>Malagueño - Cañitas</t>
-  </si>
-  <si>
-    <t>Mendiolaza - Q2</t>
-  </si>
-  <si>
-    <t>Villa ciudad parque - Molvento</t>
+    <t>Casa en Blanco</t>
+  </si>
+  <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>Casa en Blanco.xml</t>
+  </si>
+  <si>
+    <t>Local Comercial MB</t>
+  </si>
+  <si>
+    <t>Local Comercial MB.xml</t>
+  </si>
+  <si>
+    <t>Losa Herrera</t>
+  </si>
+  <si>
+    <t>Losa Herrera.xml</t>
+  </si>
+  <si>
+    <t>Oficinas Pagos 360</t>
+  </si>
+  <si>
+    <t>Oficinas Pagos 360.xml</t>
+  </si>
+  <si>
+    <t>Quincho Andrea-Bonetto</t>
+  </si>
+  <si>
+    <t>Qincho Andrea-Bonetto.xml</t>
+  </si>
+  <si>
+    <t>Vivienda Giaveno - Remodelación</t>
+  </si>
+  <si>
+    <t>Vivienda Giaveno - Remodelación.xml</t>
+  </si>
+  <si>
+    <t>Vivienda Jardin Ingles</t>
+  </si>
+  <si>
+    <t>Vivienda Jardin Ingles.xml</t>
+  </si>
+  <si>
+    <t>Vivienda La Deseada Fernando Arzola</t>
+  </si>
+  <si>
+    <t>Vivienda La Deseada Fernando Arzola.xml</t>
+  </si>
+  <si>
+    <t>Vivienda Lomas de la Carolina</t>
+  </si>
+  <si>
+    <t>Vivienda Lomas de la Carolina.xml</t>
+  </si>
+  <si>
+    <t>Vivienda Pasquali</t>
+  </si>
+  <si>
+    <t>Vivienda Pasquali.xml</t>
+  </si>
+  <si>
+    <t>Vivienda Potrerillo Fernando Arzola</t>
+  </si>
+  <si>
+    <t>Vivienda Potrerillo Fernando Arzola.xml</t>
+  </si>
+  <si>
+    <t>Vivienda Vergara</t>
+  </si>
+  <si>
+    <t>Vivienda Vergara.xml</t>
+  </si>
+  <si>
+    <t>Vivivenda Villanueva - Casa 01</t>
+  </si>
+  <si>
+    <t>Vivienda Villanueva - Casa 01.xml</t>
+  </si>
+  <si>
+    <t>Vivivenda Villanueva - Casa 02</t>
+  </si>
+  <si>
+    <t>Vivienda Villanueva - Casa 02.xml</t>
+  </si>
+  <si>
+    <t>Vivienda ODDO</t>
+  </si>
+  <si>
+    <t>Viviendas ODDO.xml</t>
+  </si>
+  <si>
+    <t>Fernando Arzola</t>
+  </si>
+  <si>
+    <t>Cancelada</t>
+  </si>
+  <si>
+    <t>Córdoba Capital</t>
+  </si>
+  <si>
+    <t>La Calera - La Deseada</t>
+  </si>
+  <si>
+    <t>Alta gracia</t>
+  </si>
+  <si>
+    <t>Villa Allende</t>
+  </si>
+  <si>
+    <t>Villa del Dique</t>
+  </si>
+  <si>
+    <t>Edificor</t>
+  </si>
+  <si>
+    <t>Maria Bacur</t>
+  </si>
+  <si>
+    <t>Blussand-Tosco</t>
+  </si>
+  <si>
+    <t>Pagos 360</t>
+  </si>
+  <si>
+    <t>Andrea Bonetto</t>
+  </si>
+  <si>
+    <t>Gabriel Giaveno</t>
+  </si>
+  <si>
+    <t>Celeste carballido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignacio </t>
+  </si>
+  <si>
+    <t>Sergio Pasquali</t>
+  </si>
+  <si>
+    <t>Lisandro Vergara</t>
+  </si>
+  <si>
+    <t>Guillermo Villanueva</t>
+  </si>
+  <si>
+    <t>Martin Oddo</t>
   </si>
 </sst>
 </file>
@@ -279,7 +426,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -302,11 +449,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -319,6 +486,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,17 +792,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
     <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -658,42 +830,42 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="3">
@@ -708,30 +880,30 @@
       <c r="J2" s="4"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5">
         <v>533.79999999999995</v>
@@ -745,30 +917,30 @@
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3">
         <v>319.20999999999998</v>
@@ -783,27 +955,27 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="5"/>
@@ -812,30 +984,30 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3">
         <v>727.55</v>
@@ -850,30 +1022,30 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G7" s="5">
         <f>367+279</f>
@@ -889,30 +1061,30 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3">
         <v>292</v>
@@ -922,24 +1094,24 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -949,30 +1121,30 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3">
         <f>241+185</f>
@@ -988,30 +1160,30 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1019,30 +1191,30 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G12" s="3">
         <f>238+78+98</f>
@@ -1058,10 +1230,355 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="L22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="L24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="L25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="L26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="L27" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/Proyectos_Bauvek.xlsx
+++ b/data/Proyectos_Bauvek.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9235E7D7-BA9D-45B0-A3E2-C159673A3E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CAB70B-F37C-49AD-8DFF-4AEE467FDA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
   <si>
     <t>Proyecto</t>
   </si>
@@ -56,331 +56,232 @@
     <t>Comitente</t>
   </si>
   <si>
+    <t>m² Terreno</t>
+  </si>
+  <si>
+    <t>Ubicación / Dirección</t>
+  </si>
+  <si>
+    <t>Contratista Principal</t>
+  </si>
+  <si>
+    <t>Archivo XML</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>Viviendas Hermanos Rossi</t>
+  </si>
+  <si>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>Obra</t>
+  </si>
+  <si>
+    <t>Córdoba</t>
+  </si>
+  <si>
+    <t>Molvento</t>
+  </si>
+  <si>
+    <t>Vivienda_Hermanos_Rossi.xml</t>
+  </si>
+  <si>
+    <t>253 tareas / 27% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Julieta Santiago</t>
+  </si>
+  <si>
+    <t>JULIETA SANTIAGO - IVAN PETRINI</t>
+  </si>
+  <si>
+    <t>Vivienda_Julieta_Santiago.xml</t>
+  </si>
+  <si>
+    <t>248 tareas / 41% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Esteban y Matías</t>
+  </si>
+  <si>
+    <t>Esteban y Matías</t>
+  </si>
+  <si>
+    <t>Vivienda_Esteban_y_Matias.xml</t>
+  </si>
+  <si>
+    <t>232 tareas / 1% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Roberto Conde</t>
+  </si>
+  <si>
+    <t>En pausa</t>
+  </si>
+  <si>
+    <t>2-En Proyecto</t>
+  </si>
+  <si>
+    <t>Vivienda_Roberto_Conde.xml</t>
+  </si>
+  <si>
+    <t>225 tareas / 7% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Lugón</t>
+  </si>
+  <si>
+    <t>RODRIGO LUGON</t>
+  </si>
+  <si>
+    <t>Vivienda_Lugon.xml</t>
+  </si>
+  <si>
+    <t>179 tareas / 1% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Reboni</t>
+  </si>
+  <si>
+    <t>Mendiolaza</t>
+  </si>
+  <si>
+    <t>Hernan Reboni</t>
+  </si>
+  <si>
+    <t>Vivienda_Reboni.xml</t>
+  </si>
+  <si>
+    <t>178 tareas / 47% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Venturelli - Bernal</t>
+  </si>
+  <si>
+    <t>Chubut</t>
+  </si>
+  <si>
+    <t>Venturelli-Bernal</t>
+  </si>
+  <si>
+    <t>Vivienda_Venturelli_-_Bernal.xml</t>
+  </si>
+  <si>
+    <t>106 tareas / 8% avance</t>
+  </si>
+  <si>
+    <t>La Vicenta</t>
+  </si>
+  <si>
+    <t>La_Vicenta.xml</t>
+  </si>
+  <si>
+    <t>49 tareas / 15% avance</t>
+  </si>
+  <si>
+    <t>Vivienda AZ</t>
+  </si>
+  <si>
+    <t>Agustin Zampol</t>
+  </si>
+  <si>
+    <t>Vivienda_AZ.xml</t>
+  </si>
+  <si>
+    <t>32 tareas / 0% avance</t>
+  </si>
+  <si>
+    <t>Losa Mogetta</t>
+  </si>
+  <si>
+    <t>Losa_Mogetta.xml</t>
+  </si>
+  <si>
+    <t>19 tareas / 87% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Lew-Subías</t>
+  </si>
+  <si>
+    <t>Rodolfo Subias y Melisa Lew</t>
+  </si>
+  <si>
+    <t>Vivienda_Lew-Subias.xml</t>
+  </si>
+  <si>
+    <t>5 tareas / 24% avance</t>
+  </si>
+  <si>
+    <t>m² Construidos semicubierta</t>
+  </si>
+  <si>
     <t>m² Construidos cubierta</t>
   </si>
   <si>
-    <t>m² Construidos semicubierta</t>
-  </si>
-  <si>
-    <t>m² Terreno</t>
-  </si>
-  <si>
-    <t>Ubicación / Dirección</t>
-  </si>
-  <si>
-    <t>Contratista Principal</t>
-  </si>
-  <si>
-    <t>Archivo XML</t>
-  </si>
-  <si>
-    <t>Notas</t>
-  </si>
-  <si>
-    <t>Viviendas Hermanos Rossi</t>
-  </si>
-  <si>
-    <t>Activo</t>
-  </si>
-  <si>
-    <t>Obra</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
+    <t>Mendiolaza - El terrón</t>
+  </si>
+  <si>
+    <t>La Calera - Vistas de la Deseada</t>
+  </si>
+  <si>
+    <t>Malagueño - Cañitas</t>
+  </si>
+  <si>
+    <t>Mendiolaza - Q2</t>
   </si>
   <si>
     <t>Villa ciudad parque - Molvento</t>
   </si>
   <si>
-    <t>Vivienda Hermanos Rossi.xml</t>
-  </si>
-  <si>
-    <t>253 tareas / 27% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Julieta Santiago</t>
-  </si>
-  <si>
-    <t>JULIETA SANTIAGO - IVAN PETRINI</t>
-  </si>
-  <si>
-    <t>Vivienda Julieta Santiago.xml</t>
-  </si>
-  <si>
-    <t>248 tareas / 41% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Esteban y Matías</t>
-  </si>
-  <si>
-    <t>La Calera - Vistas de la Deseada</t>
-  </si>
-  <si>
-    <t>Esteban y Matías</t>
-  </si>
-  <si>
-    <t>Vivienda Esteban y Matias.xml</t>
-  </si>
-  <si>
-    <t>232 tareas / 1% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Roberto Conde</t>
-  </si>
-  <si>
-    <t>En pausa</t>
-  </si>
-  <si>
-    <t>2-En Proyecto</t>
-  </si>
-  <si>
-    <t>Molvento</t>
-  </si>
-  <si>
-    <t>Vivienda RC.xml</t>
-  </si>
-  <si>
-    <t>225 tareas / 7% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Lugón</t>
-  </si>
-  <si>
-    <t>Mendiolaza - Q2</t>
-  </si>
-  <si>
-    <t>RODRIGO LUGON</t>
-  </si>
-  <si>
-    <t>Vivienda Lugon.xml</t>
-  </si>
-  <si>
-    <t>179 tareas / 1% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Reboni</t>
-  </si>
-  <si>
-    <t>Mendiolaza - El terrón</t>
-  </si>
-  <si>
-    <t>Hernan Reboni</t>
-  </si>
-  <si>
-    <t>Vivienda Reboni.xml</t>
-  </si>
-  <si>
-    <t>178 tareas / 47% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Venturelli - Bernal</t>
-  </si>
-  <si>
-    <t>Chubut</t>
-  </si>
-  <si>
-    <t>Malagueño - Cañitas</t>
-  </si>
-  <si>
-    <t>Venturelli-Bernal</t>
-  </si>
-  <si>
-    <t>Vivienda Venturelli-Bernal.xml</t>
-  </si>
-  <si>
-    <t>106 tareas / 8% avance</t>
-  </si>
-  <si>
-    <t>La Vicenta</t>
-  </si>
-  <si>
-    <t>Loteo - La Vicenta.xml</t>
-  </si>
-  <si>
-    <t>49 tareas / 15% avance</t>
-  </si>
-  <si>
-    <t>Vivienda AZ</t>
-  </si>
-  <si>
-    <t>Agustin Zampol</t>
-  </si>
-  <si>
-    <t>Vivienda AZ.xml</t>
-  </si>
-  <si>
-    <t>32 tareas / 0% avance</t>
-  </si>
-  <si>
-    <t>Losa Mogetta</t>
-  </si>
-  <si>
-    <t>Losa Mogetta.xml</t>
-  </si>
-  <si>
-    <t>19 tareas / 87% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Lew-Subías</t>
-  </si>
-  <si>
-    <t>Rodolfo Subias y Melisa Lew</t>
-  </si>
-  <si>
-    <t>Vivienda Lew-Subias.xml</t>
-  </si>
-  <si>
-    <t>5 tareas / 24% avance</t>
-  </si>
-  <si>
     <t>Casa en Blanco</t>
   </si>
   <si>
+    <t>Local Comercial MB</t>
+  </si>
+  <si>
+    <t>Losa Herrera</t>
+  </si>
+  <si>
+    <t>Oficinas Pagos 360</t>
+  </si>
+  <si>
+    <t>Quincho Andrea-Bonetto</t>
+  </si>
+  <si>
+    <t>Vivienda Giaveno - Remodelación</t>
+  </si>
+  <si>
+    <t>Vivienda Jardin Ingles</t>
+  </si>
+  <si>
+    <t>Vivienda La Deseada Fernando Arzola</t>
+  </si>
+  <si>
+    <t>Vivienda Lomas de la Carolina</t>
+  </si>
+  <si>
+    <t>Vivienda Pasquali</t>
+  </si>
+  <si>
+    <t>Vivienda Potrerillo Fernando Arzola</t>
+  </si>
+  <si>
+    <t>Vivienda Vergara</t>
+  </si>
+  <si>
+    <t>Vivivenda Villanueva - Casa 01</t>
+  </si>
+  <si>
+    <t>Vivienda ODDO</t>
+  </si>
+  <si>
+    <t>Vivivenda Villanueva - Casa 02</t>
+  </si>
+  <si>
     <t>Finalizado</t>
-  </si>
-  <si>
-    <t>Casa en Blanco.xml</t>
-  </si>
-  <si>
-    <t>Local Comercial MB</t>
-  </si>
-  <si>
-    <t>Local Comercial MB.xml</t>
-  </si>
-  <si>
-    <t>Losa Herrera</t>
-  </si>
-  <si>
-    <t>Losa Herrera.xml</t>
-  </si>
-  <si>
-    <t>Oficinas Pagos 360</t>
-  </si>
-  <si>
-    <t>Oficinas Pagos 360.xml</t>
-  </si>
-  <si>
-    <t>Quincho Andrea-Bonetto</t>
-  </si>
-  <si>
-    <t>Qincho Andrea-Bonetto.xml</t>
-  </si>
-  <si>
-    <t>Vivienda Giaveno - Remodelación</t>
-  </si>
-  <si>
-    <t>Vivienda Giaveno - Remodelación.xml</t>
-  </si>
-  <si>
-    <t>Vivienda Jardin Ingles</t>
-  </si>
-  <si>
-    <t>Vivienda Jardin Ingles.xml</t>
-  </si>
-  <si>
-    <t>Vivienda La Deseada Fernando Arzola</t>
-  </si>
-  <si>
-    <t>Vivienda La Deseada Fernando Arzola.xml</t>
-  </si>
-  <si>
-    <t>Vivienda Lomas de la Carolina</t>
-  </si>
-  <si>
-    <t>Vivienda Lomas de la Carolina.xml</t>
-  </si>
-  <si>
-    <t>Vivienda Pasquali</t>
-  </si>
-  <si>
-    <t>Vivienda Pasquali.xml</t>
-  </si>
-  <si>
-    <t>Vivienda Potrerillo Fernando Arzola</t>
-  </si>
-  <si>
-    <t>Vivienda Potrerillo Fernando Arzola.xml</t>
-  </si>
-  <si>
-    <t>Vivienda Vergara</t>
-  </si>
-  <si>
-    <t>Vivienda Vergara.xml</t>
-  </si>
-  <si>
-    <t>Vivivenda Villanueva - Casa 01</t>
-  </si>
-  <si>
-    <t>Vivienda Villanueva - Casa 01.xml</t>
-  </si>
-  <si>
-    <t>Vivivenda Villanueva - Casa 02</t>
-  </si>
-  <si>
-    <t>Vivienda Villanueva - Casa 02.xml</t>
-  </si>
-  <si>
-    <t>Vivienda ODDO</t>
-  </si>
-  <si>
-    <t>Viviendas ODDO.xml</t>
-  </si>
-  <si>
-    <t>Fernando Arzola</t>
-  </si>
-  <si>
-    <t>Cancelada</t>
-  </si>
-  <si>
-    <t>Córdoba Capital</t>
-  </si>
-  <si>
-    <t>La Calera - La Deseada</t>
-  </si>
-  <si>
-    <t>Alta gracia</t>
-  </si>
-  <si>
-    <t>Villa Allende</t>
-  </si>
-  <si>
-    <t>Villa del Dique</t>
-  </si>
-  <si>
-    <t>Edificor</t>
-  </si>
-  <si>
-    <t>Maria Bacur</t>
-  </si>
-  <si>
-    <t>Blussand-Tosco</t>
-  </si>
-  <si>
-    <t>Pagos 360</t>
-  </si>
-  <si>
-    <t>Andrea Bonetto</t>
-  </si>
-  <si>
-    <t>Gabriel Giaveno</t>
-  </si>
-  <si>
-    <t>Celeste carballido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignacio </t>
-  </si>
-  <si>
-    <t>Sergio Pasquali</t>
-  </si>
-  <si>
-    <t>Lisandro Vergara</t>
-  </si>
-  <si>
-    <t>Guillermo Villanueva</t>
-  </si>
-  <si>
-    <t>Martin Oddo</t>
   </si>
 </sst>
 </file>
@@ -426,7 +327,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -460,20 +361,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -486,10 +378,8 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,11 +689,10 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="38.109375" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="21.88671875" customWidth="1"/>
-    <col min="8" max="8" width="25.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -830,42 +719,42 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="3">
@@ -880,30 +769,30 @@
       <c r="J2" s="4"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" s="5">
         <v>533.79999999999995</v>
@@ -917,30 +806,30 @@
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3">
         <v>319.20999999999998</v>
@@ -955,27 +844,27 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="5"/>
@@ -984,30 +873,30 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G6" s="3">
         <v>727.55</v>
@@ -1022,30 +911,30 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G7" s="5">
         <f>367+279</f>
@@ -1061,30 +950,30 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G8" s="3">
         <v>292</v>
@@ -1094,24 +983,24 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1121,30 +1010,30 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G10" s="3">
         <f>241+185</f>
@@ -1160,30 +1049,30 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="E11" s="4" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1191,30 +1080,30 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3">
         <f>238+78+98</f>
@@ -1230,355 +1119,130 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L15" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="B19" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="B20" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="B21" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="B22" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="L18" t="s">
+      <c r="B23" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="B24" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="B25" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="L21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="L24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="L25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="L26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="B27" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="L27" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/Proyectos_Bauvek.xlsx
+++ b/data/Proyectos_Bauvek.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CAB70B-F37C-49AD-8DFF-4AEE467FDA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF40073-19AE-4680-B416-2880E1F9412D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$M$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="119">
   <si>
     <t>Proyecto</t>
   </si>
@@ -56,6 +56,12 @@
     <t>Comitente</t>
   </si>
   <si>
+    <t>m² Construidos cubierta</t>
+  </si>
+  <si>
+    <t>m² Construidos semicubierta</t>
+  </si>
+  <si>
     <t>m² Terreno</t>
   </si>
   <si>
@@ -83,49 +89,55 @@
     <t>Córdoba</t>
   </si>
   <si>
+    <t>Villa ciudad parque - Molvento</t>
+  </si>
+  <si>
+    <t>Vivienda Hermanos Rossi.xml</t>
+  </si>
+  <si>
+    <t>253 tareas / 27% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Julieta Santiago</t>
+  </si>
+  <si>
+    <t>JULIETA SANTIAGO - IVAN PETRINI</t>
+  </si>
+  <si>
+    <t>Vivienda Julieta Santiago.xml</t>
+  </si>
+  <si>
+    <t>248 tareas / 41% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Esteban y Matías</t>
+  </si>
+  <si>
+    <t>La Calera - Vistas de la Deseada</t>
+  </si>
+  <si>
+    <t>Esteban y Matías</t>
+  </si>
+  <si>
+    <t>Vivienda Esteban y Matias.xml</t>
+  </si>
+  <si>
+    <t>232 tareas / 1% avance</t>
+  </si>
+  <si>
+    <t>Vivienda Roberto Conde</t>
+  </si>
+  <si>
+    <t>En pausa</t>
+  </si>
+  <si>
+    <t>2-En Proyecto</t>
+  </si>
+  <si>
     <t>Molvento</t>
   </si>
   <si>
-    <t>Vivienda_Hermanos_Rossi.xml</t>
-  </si>
-  <si>
-    <t>253 tareas / 27% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Julieta Santiago</t>
-  </si>
-  <si>
-    <t>JULIETA SANTIAGO - IVAN PETRINI</t>
-  </si>
-  <si>
-    <t>Vivienda_Julieta_Santiago.xml</t>
-  </si>
-  <si>
-    <t>248 tareas / 41% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Esteban y Matías</t>
-  </si>
-  <si>
-    <t>Esteban y Matías</t>
-  </si>
-  <si>
-    <t>Vivienda_Esteban_y_Matias.xml</t>
-  </si>
-  <si>
-    <t>232 tareas / 1% avance</t>
-  </si>
-  <si>
-    <t>Vivienda Roberto Conde</t>
-  </si>
-  <si>
-    <t>En pausa</t>
-  </si>
-  <si>
-    <t>2-En Proyecto</t>
-  </si>
-  <si>
-    <t>Vivienda_Roberto_Conde.xml</t>
+    <t>Vivienda RC.xml</t>
   </si>
   <si>
     <t>225 tareas / 7% avance</t>
@@ -134,10 +146,13 @@
     <t>Vivienda Lugón</t>
   </si>
   <si>
+    <t>Mendiolaza - Q2</t>
+  </si>
+  <si>
     <t>RODRIGO LUGON</t>
   </si>
   <si>
-    <t>Vivienda_Lugon.xml</t>
+    <t>Vivienda Lugon.xml</t>
   </si>
   <si>
     <t>179 tareas / 1% avance</t>
@@ -146,13 +161,13 @@
     <t>Vivienda Reboni</t>
   </si>
   <si>
-    <t>Mendiolaza</t>
+    <t>Mendiolaza - El terrón</t>
   </si>
   <si>
     <t>Hernan Reboni</t>
   </si>
   <si>
-    <t>Vivienda_Reboni.xml</t>
+    <t>Vivienda Reboni.xml</t>
   </si>
   <si>
     <t>178 tareas / 47% avance</t>
@@ -164,10 +179,13 @@
     <t>Chubut</t>
   </si>
   <si>
+    <t>Malagueño - Cañitas</t>
+  </si>
+  <si>
     <t>Venturelli-Bernal</t>
   </si>
   <si>
-    <t>Vivienda_Venturelli_-_Bernal.xml</t>
+    <t>Vivienda Venturelli-Bernal.xml</t>
   </si>
   <si>
     <t>106 tareas / 8% avance</t>
@@ -176,7 +194,7 @@
     <t>La Vicenta</t>
   </si>
   <si>
-    <t>La_Vicenta.xml</t>
+    <t>Loteo - La Vicenta.xml</t>
   </si>
   <si>
     <t>49 tareas / 15% avance</t>
@@ -188,7 +206,7 @@
     <t>Agustin Zampol</t>
   </si>
   <si>
-    <t>Vivienda_AZ.xml</t>
+    <t>Vivienda AZ.xml</t>
   </si>
   <si>
     <t>32 tareas / 0% avance</t>
@@ -197,7 +215,7 @@
     <t>Losa Mogetta</t>
   </si>
   <si>
-    <t>Losa_Mogetta.xml</t>
+    <t>Losa Mogetta.xml</t>
   </si>
   <si>
     <t>19 tareas / 87% avance</t>
@@ -209,79 +227,172 @@
     <t>Rodolfo Subias y Melisa Lew</t>
   </si>
   <si>
-    <t>Vivienda_Lew-Subias.xml</t>
+    <t>Vivienda Lew-Subias.xml</t>
   </si>
   <si>
     <t>5 tareas / 24% avance</t>
   </si>
   <si>
-    <t>m² Construidos semicubierta</t>
-  </si>
-  <si>
-    <t>m² Construidos cubierta</t>
-  </si>
-  <si>
-    <t>Mendiolaza - El terrón</t>
-  </si>
-  <si>
-    <t>La Calera - Vistas de la Deseada</t>
-  </si>
-  <si>
-    <t>Malagueño - Cañitas</t>
-  </si>
-  <si>
-    <t>Mendiolaza - Q2</t>
-  </si>
-  <si>
-    <t>Villa ciudad parque - Molvento</t>
-  </si>
-  <si>
     <t>Casa en Blanco</t>
   </si>
   <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>Casa en Blanco.xml</t>
+  </si>
+  <si>
     <t>Local Comercial MB</t>
   </si>
   <si>
+    <t>Local Comercial MB.xml</t>
+  </si>
+  <si>
     <t>Losa Herrera</t>
   </si>
   <si>
+    <t>Losa Herrera.xml</t>
+  </si>
+  <si>
     <t>Oficinas Pagos 360</t>
   </si>
   <si>
+    <t>Oficinas Pagos 360.xml</t>
+  </si>
+  <si>
     <t>Quincho Andrea-Bonetto</t>
   </si>
   <si>
+    <t>Qincho Andrea-Bonetto.xml</t>
+  </si>
+  <si>
     <t>Vivienda Giaveno - Remodelación</t>
   </si>
   <si>
+    <t>Vivienda Giaveno - Remodelación.xml</t>
+  </si>
+  <si>
     <t>Vivienda Jardin Ingles</t>
   </si>
   <si>
+    <t>Vivienda Jardin Ingles.xml</t>
+  </si>
+  <si>
     <t>Vivienda La Deseada Fernando Arzola</t>
   </si>
   <si>
+    <t>Vivienda La Deseada Fernando Arzola.xml</t>
+  </si>
+  <si>
     <t>Vivienda Lomas de la Carolina</t>
   </si>
   <si>
+    <t>Vivienda Lomas de la Carolina.xml</t>
+  </si>
+  <si>
     <t>Vivienda Pasquali</t>
   </si>
   <si>
+    <t>Vivienda Pasquali.xml</t>
+  </si>
+  <si>
     <t>Vivienda Potrerillo Fernando Arzola</t>
   </si>
   <si>
+    <t>Vivienda Potrerillo Fernando Arzola.xml</t>
+  </si>
+  <si>
     <t>Vivienda Vergara</t>
   </si>
   <si>
+    <t>Vivienda Vergara.xml</t>
+  </si>
+  <si>
     <t>Vivivenda Villanueva - Casa 01</t>
   </si>
   <si>
+    <t>Vivienda Villanueva - Casa 01.xml</t>
+  </si>
+  <si>
+    <t>Vivivenda Villanueva - Casa 02</t>
+  </si>
+  <si>
+    <t>Vivienda Villanueva - Casa 02.xml</t>
+  </si>
+  <si>
     <t>Vivienda ODDO</t>
   </si>
   <si>
-    <t>Vivivenda Villanueva - Casa 02</t>
-  </si>
-  <si>
-    <t>Finalizado</t>
+    <t>Viviendas ODDO.xml</t>
+  </si>
+  <si>
+    <t>Fernando Arzola</t>
+  </si>
+  <si>
+    <t>Cancelada</t>
+  </si>
+  <si>
+    <t>Córdoba Capital</t>
+  </si>
+  <si>
+    <t>La Calera - La Deseada</t>
+  </si>
+  <si>
+    <t>Alta gracia</t>
+  </si>
+  <si>
+    <t>Villa Allende</t>
+  </si>
+  <si>
+    <t>Villa del Dique</t>
+  </si>
+  <si>
+    <t>Edificor</t>
+  </si>
+  <si>
+    <t>Maria Bacur</t>
+  </si>
+  <si>
+    <t>Blussand-Tosco</t>
+  </si>
+  <si>
+    <t>Pagos 360</t>
+  </si>
+  <si>
+    <t>Andrea Bonetto</t>
+  </si>
+  <si>
+    <t>Gabriel Giaveno</t>
+  </si>
+  <si>
+    <t>Celeste carballido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignacio </t>
+  </si>
+  <si>
+    <t>Sergio Pasquali</t>
+  </si>
+  <si>
+    <t>Lisandro Vergara</t>
+  </si>
+  <si>
+    <t>Guillermo Villanueva</t>
+  </si>
+  <si>
+    <t>Martin Oddo</t>
+  </si>
+  <si>
+    <t>Vivienda Carola Ruda</t>
+  </si>
+  <si>
+    <t>Carola Ruda</t>
+  </si>
+  <si>
+    <t>Vivienda Casali D</t>
+  </si>
+  <si>
+    <t>Diego Casali</t>
   </si>
 </sst>
 </file>
@@ -327,7 +438,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -361,11 +472,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -378,8 +498,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,17 +804,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
     <col min="10" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
@@ -719,42 +842,42 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="3">
@@ -769,484 +892,759 @@
       <c r="J2" s="4"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="5">
         <v>533.79999999999995</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H5" s="5">
         <f>65.36</f>
         <v>65.36</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I5" s="5">
         <v>4601</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="M5" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="3">
         <v>319.20999999999998</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H6" s="3">
         <f>53.23+56.23</f>
         <v>109.46</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I6" s="3">
         <v>1382.23</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="3">
-        <v>727.55</v>
-      </c>
-      <c r="H6" s="3">
-        <f>10.35+43.3</f>
-        <v>53.65</v>
-      </c>
-      <c r="I6" s="3">
-        <v>2039</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="5">
-        <f>367+279</f>
-        <v>646</v>
-      </c>
-      <c r="H7" s="5">
-        <f>88+7</f>
-        <v>95</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1739.16</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3">
-        <v>292</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <v>727.55</v>
+      </c>
+      <c r="H8" s="3">
+        <f>10.35+43.3</f>
+        <v>53.65</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2039</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="5">
+        <f>367+279</f>
+        <v>646</v>
+      </c>
+      <c r="H9" s="5">
+        <f>88+7</f>
+        <v>95</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1739.16</v>
+      </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="G10" s="3">
-        <f>241+185</f>
-        <v>426</v>
-      </c>
-      <c r="H10" s="3">
-        <f>18.7+45</f>
-        <v>63.7</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1153.8699999999999</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G12" s="3">
-        <f>238+78+98</f>
-        <v>414</v>
+        <f>241+185</f>
+        <v>426</v>
       </c>
       <c r="H12" s="3">
-        <f>71+31</f>
-        <v>102</v>
+        <f>18.7+45</f>
+        <v>63.7</v>
       </c>
       <c r="I12" s="3">
-        <v>1368</v>
+        <v>1153.8699999999999</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>81</v>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>81</v>
+      <c r="A14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="3">
+        <f>238+78+98</f>
+        <v>414</v>
+      </c>
+      <c r="H14" s="3">
+        <f>71+31</f>
+        <v>102</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1368</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L16" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="L19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="L20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="L24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>80</v>
+        <v>97</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>79</v>
+        <v>66</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>81</v>
+        <v>97</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="L28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L29" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>